--- a/src/assets/傳票範本.xlsx
+++ b/src/assets/傳票範本.xlsx
@@ -15,7 +15,7 @@
     <sheet name="工作表" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">工作表!$9:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">工作表!$4:$9</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
